--- a/examples/bank.xlsx
+++ b/examples/bank.xlsx
@@ -505,11 +505,11 @@
         <v>46042</v>
       </c>
       <c r="B5" t="n">
-        <v>1184</v>
+        <v>409.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">GENEVIEVE BELHADJ      	2026-008	BGC	</t>
+          <t xml:space="preserve">MARGIT PELLETIER       	2026-008	BGC	</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -965,11 +965,11 @@
         <v>46070</v>
       </c>
       <c r="B28" t="n">
-        <v>434.5</v>
+        <v>774.5</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">KATRIN BEAUCHAMP       	2026-008	BGC	</t>
+          <t xml:space="preserve">GENEVIEVE BELHADJ      	2026-008	BGC	</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1665,7 +1665,7 @@
         <v>46133</v>
       </c>
       <c r="B63" t="n">
-        <v>347</v>
+        <v>359.5</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>46143</v>
       </c>
       <c r="B74" t="n">
-        <v>592</v>
+        <v>204.75</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>46168</v>
       </c>
       <c r="B76" t="n">
-        <v>347</v>
+        <v>359.5</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>46170</v>
       </c>
       <c r="B77" t="n">
-        <v>592</v>
+        <v>204.75</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
